--- a/case_study_1_commonality.xlsx
+++ b/case_study_1_commonality.xlsx
@@ -1,34 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>LV</t>
+  </si>
+  <si>
+    <t>n_1SE</t>
+  </si>
+  <si>
+    <t>Q2_full</t>
+  </si>
+  <si>
+    <t>joint</t>
+  </si>
+  <si>
+    <t>uM</t>
+  </si>
+  <si>
+    <t>uX</t>
+  </si>
+  <si>
+    <t>shared</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>shared_frac</t>
+  </si>
+  <si>
+    <t>coverage</t>
+  </si>
+  <si>
+    <t>fit_cost</t>
+  </si>
+  <si>
+    <t>roll_R2e</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>M0_correct</t>
+  </si>
+  <si>
+    <t>M1_no_side</t>
+  </si>
+  <si>
+    <t>M2_order1_D</t>
+  </si>
+  <si>
+    <t>M3_wrong_Ea4</t>
+  </si>
+  <si>
+    <t>M4_lumped_EF</t>
+  </si>
+  <si>
+    <t>M5_no_D</t>
+  </si>
+  <si>
+    <t>M6_author_mis</t>
+  </si>
+  <si>
+    <t>(1,4,5)</t>
+  </si>
+  <si>
+    <t>(1,3,5)</t>
+  </si>
+  <si>
+    <t>(1,3,6)</t>
+  </si>
+  <si>
+    <t>(1,4,4)</t>
+  </si>
+  <si>
+    <t>(1,5,2)</t>
+  </si>
+  <si>
+    <t>(1,3,7)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +128,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,371 +422,339 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>n_1SE</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Q2_full</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>uM</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>uX</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>shared_frac</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>coverage</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>fit_cost</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>M0_correct</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>(1,4,5)</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2">
         <v>243</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.912992085093364</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.7953522760731877</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.2542739190864974</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.1374702072336589</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0.4036081497530314</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>1.849665641765613</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0.5074583450565139</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>0.4925416549434861</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>201493.7037749742</v>
       </c>
+      <c r="M2">
+        <v>0.5886942615613514</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>M1_no_side</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>(1,3,5)</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3">
         <v>100</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.9145273593138338</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.7968875502936574</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.2558091933069672</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.200758388967621</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0.3403199680190693</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>1.274214216513886</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>0.4270614692043557</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>0.5729385307956443</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>2914586.646135744</v>
       </c>
+      <c r="M3">
+        <v>-1.675462181064448</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>M2_order1_D</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>(1,3,6)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4">
         <v>195</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>0.9075288542372912</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.7898890452171149</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.1846047151930683</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.155407732143096</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0.4498765978809506</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>1.187873425905787</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>0.5695440398939754</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>0.4304559601060247</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>1382712.759595139</v>
       </c>
+      <c r="M4">
+        <v>0.4277416325302397</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>M3_wrong_Ea4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>(1,4,4)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
         <v>258</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.9096144620286818</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0.7919746530085054</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.2730473078154586</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.1450863613926191</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>0.3738409838004277</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>1.881963991615749</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>0.4720365511450438</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>0.5279634488549562</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>205413.4668500866</v>
       </c>
+      <c r="M5">
+        <v>0.6278577952525886</v>
+      </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>M4_lumped_EF</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>(1,5,2)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
         <v>358</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.9071136881867456</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.7894738791665693</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0.3836430380279461</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>0.1174138629975086</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>0.2884169781411147</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>3.267442431700648</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>0.3653280820963833</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>0.6346719179036167</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>980218.7969960317</v>
       </c>
+      <c r="M6">
+        <v>0.4315814893130882</v>
+      </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>M5_no_D</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>(1,3,7)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7">
         <v>130</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>0.9046087365603656</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.7869689275401892</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0.1544355660725124</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>0.4286566208416185</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>0.2038767406260583</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>0.360278037393417</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>0.2590658074179767</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>0.7409341925820233</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>10974643.81545921</v>
       </c>
+      <c r="M7">
+        <v>-16.45331330349336</v>
+      </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>M6_author_mis</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>(1,3,5)</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
         <v>424</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>0.9041151630655522</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.7864753540453758</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>0.2453969970586856</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>0.1613881170012201</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>0.3796902399854701</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>1.520539440068133</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>0.4827744925921275</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>0.5172255074078725</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>3809140.869737337</v>
+      </c>
+      <c r="M8">
+        <v>-1.566202392302754</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/case_study_1_commonality.xlsx
+++ b/case_study_1_commonality.xlsx
@@ -478,28 +478,28 @@
         <v>243</v>
       </c>
       <c r="D2">
-        <v>0.912992085093364</v>
+        <v>0.9129920850933639</v>
       </c>
       <c r="E2">
-        <v>0.7953522760731877</v>
+        <v>0.7953522760731875</v>
       </c>
       <c r="F2">
-        <v>0.2542739190864974</v>
+        <v>0.190067946049141</v>
       </c>
       <c r="G2">
-        <v>0.1374702072336589</v>
+        <v>0.05260074452554209</v>
       </c>
       <c r="H2">
-        <v>0.4036081497530314</v>
+        <v>0.5526835854985044</v>
       </c>
       <c r="I2">
-        <v>1.849665641765613</v>
+        <v>3.613407904461258</v>
       </c>
       <c r="J2">
-        <v>0.5074583450565139</v>
+        <v>0.6948915620474656</v>
       </c>
       <c r="K2">
-        <v>0.4925416549434861</v>
+        <v>0.3051084379525343</v>
       </c>
       <c r="L2">
         <v>201493.7037749742</v>
@@ -522,25 +522,25 @@
         <v>0.9145273593138338</v>
       </c>
       <c r="E3">
-        <v>0.7968875502936574</v>
+        <v>0.7968875502936573</v>
       </c>
       <c r="F3">
-        <v>0.2558091933069672</v>
+        <v>0.1916032202696109</v>
       </c>
       <c r="G3">
-        <v>0.200758388967621</v>
+        <v>0.0852574856379944</v>
       </c>
       <c r="H3">
-        <v>0.3403199680190693</v>
+        <v>0.5200268443860521</v>
       </c>
       <c r="I3">
-        <v>1.274214216513886</v>
+        <v>2.247347770530828</v>
       </c>
       <c r="J3">
-        <v>0.4270614692043557</v>
+        <v>0.6525724290640749</v>
       </c>
       <c r="K3">
-        <v>0.5729385307956443</v>
+        <v>0.3474275709359251</v>
       </c>
       <c r="L3">
         <v>2914586.646135744</v>
@@ -560,28 +560,28 @@
         <v>195</v>
       </c>
       <c r="D4">
-        <v>0.9075288542372912</v>
+        <v>0.9075288542372913</v>
       </c>
       <c r="E4">
         <v>0.7898890452171149</v>
       </c>
       <c r="F4">
-        <v>0.1846047151930683</v>
+        <v>0.1846047151930684</v>
       </c>
       <c r="G4">
-        <v>0.155407732143096</v>
+        <v>0.05653877959075881</v>
       </c>
       <c r="H4">
-        <v>0.4498765978809506</v>
+        <v>0.5487455504332877</v>
       </c>
       <c r="I4">
-        <v>1.187873425905787</v>
+        <v>3.265099044041655</v>
       </c>
       <c r="J4">
-        <v>0.5695440398939754</v>
+        <v>0.6947121924984481</v>
       </c>
       <c r="K4">
-        <v>0.4304559601060247</v>
+        <v>0.3052878075015519</v>
       </c>
       <c r="L4">
         <v>1382712.759595139</v>
@@ -601,28 +601,28 @@
         <v>258</v>
       </c>
       <c r="D5">
-        <v>0.9096144620286818</v>
+        <v>0.9096144620286819</v>
       </c>
       <c r="E5">
         <v>0.7919746530085054</v>
       </c>
       <c r="F5">
-        <v>0.2730473078154586</v>
+        <v>0.186690322984459</v>
       </c>
       <c r="G5">
-        <v>0.1450863613926191</v>
+        <v>0.04998787411383487</v>
       </c>
       <c r="H5">
-        <v>0.3738409838004277</v>
+        <v>0.5552964559102116</v>
       </c>
       <c r="I5">
-        <v>1.881963991615749</v>
+        <v>3.734712193587558</v>
       </c>
       <c r="J5">
-        <v>0.4720365511450438</v>
+        <v>0.701154328362385</v>
       </c>
       <c r="K5">
-        <v>0.5279634488549562</v>
+        <v>0.2988456716376149</v>
       </c>
       <c r="L5">
         <v>205413.4668500866</v>
@@ -642,28 +642,28 @@
         <v>358</v>
       </c>
       <c r="D6">
-        <v>0.9071136881867456</v>
+        <v>0.9071136881867459</v>
       </c>
       <c r="E6">
-        <v>0.7894738791665693</v>
+        <v>0.7894738791665694</v>
       </c>
       <c r="F6">
-        <v>0.3836430380279461</v>
+        <v>0.1841895491425229</v>
       </c>
       <c r="G6">
-        <v>0.1174138629975086</v>
+        <v>0.05716632397711896</v>
       </c>
       <c r="H6">
-        <v>0.2884169781411147</v>
+        <v>0.5481180060469275</v>
       </c>
       <c r="I6">
-        <v>3.267442431700648</v>
+        <v>3.221993935034996</v>
       </c>
       <c r="J6">
-        <v>0.3653280820963833</v>
+        <v>0.6942826362102872</v>
       </c>
       <c r="K6">
-        <v>0.6346719179036167</v>
+        <v>0.3057173637897129</v>
       </c>
       <c r="L6">
         <v>980218.7969960317</v>
@@ -686,25 +686,25 @@
         <v>0.9046087365603656</v>
       </c>
       <c r="E7">
-        <v>0.7869689275401892</v>
+        <v>0.7869689275401891</v>
       </c>
       <c r="F7">
-        <v>0.1544355660725124</v>
+        <v>0.1816845975161426</v>
       </c>
       <c r="G7">
-        <v>0.4286566208416185</v>
+        <v>0.4286566208416186</v>
       </c>
       <c r="H7">
-        <v>0.2038767406260583</v>
+        <v>0.1766277091824279</v>
       </c>
       <c r="I7">
-        <v>0.360278037393417</v>
+        <v>0.4238464745031246</v>
       </c>
       <c r="J7">
-        <v>0.2590658074179767</v>
+        <v>0.2244405121997753</v>
       </c>
       <c r="K7">
-        <v>0.7409341925820233</v>
+        <v>0.7755594878002248</v>
       </c>
       <c r="L7">
         <v>10974643.81545921</v>
@@ -724,28 +724,28 @@
         <v>424</v>
       </c>
       <c r="D8">
-        <v>0.9041151630655522</v>
+        <v>0.9041151630655523</v>
       </c>
       <c r="E8">
         <v>0.7864753540453758</v>
       </c>
       <c r="F8">
-        <v>0.2453969970586856</v>
+        <v>0.1811910240213294</v>
       </c>
       <c r="G8">
-        <v>0.1613881170012201</v>
+        <v>0.102859343099326</v>
       </c>
       <c r="H8">
-        <v>0.3796902399854701</v>
+        <v>0.5024249869247205</v>
       </c>
       <c r="I8">
-        <v>1.520539440068133</v>
+        <v>1.761541718639623</v>
       </c>
       <c r="J8">
-        <v>0.4827744925921275</v>
+        <v>0.6388311907555758</v>
       </c>
       <c r="K8">
-        <v>0.5172255074078725</v>
+        <v>0.3611688092444242</v>
       </c>
       <c r="L8">
         <v>3809140.869737337</v>
